--- a/backend/src/main/resources/db/seed/files/account-info-fee-precheck.xlsx
+++ b/backend/src/main/resources/db/seed/files/account-info-fee-precheck.xlsx
@@ -468,7 +468,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J12"/>
+  <dimension ref="A1:J11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -673,12 +673,12 @@
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>103</t>
+          <t>050</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>SBI저축은행</t>
+          <t>저축은행중앙회</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
@@ -687,36 +687,36 @@
         </is>
       </c>
       <c r="D9" s="6" t="n">
-        <v>186400</v>
+        <v>94200</v>
       </c>
       <c r="E9" s="6" t="n">
-        <v>191700</v>
+        <v>97800</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>188300</v>
+        <v>95100</v>
       </c>
       <c r="G9" s="6" t="n">
-        <v>566400</v>
+        <v>287100</v>
       </c>
       <c r="H9" s="6" t="n">
         <v>300000</v>
       </c>
       <c r="I9" s="6" t="n">
-        <v>1132800</v>
+        <v>574200</v>
       </c>
       <c r="J9" s="6" t="n">
-        <v>1432800</v>
+        <v>874200</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>050</t>
+          <t>048</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>저축은행중앙회</t>
+          <t>신협</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
@@ -725,98 +725,60 @@
         </is>
       </c>
       <c r="D10" s="6" t="n">
-        <v>94200</v>
+        <v>153900</v>
       </c>
       <c r="E10" s="6" t="n">
-        <v>97800</v>
+        <v>149600</v>
       </c>
       <c r="F10" s="6" t="n">
-        <v>95100</v>
+        <v>158200</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>287100</v>
+        <v>461700</v>
       </c>
       <c r="H10" s="6" t="n">
         <v>300000</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>574200</v>
+        <v>923400</v>
       </c>
       <c r="J10" s="6" t="n">
-        <v>874200</v>
+        <v>1223400</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="inlineStr">
-        <is>
-          <t>048</t>
-        </is>
-      </c>
-      <c r="B11" s="5" t="inlineStr">
-        <is>
-          <t>신협</t>
-        </is>
-      </c>
-      <c r="C11" s="4" t="inlineStr">
-        <is>
-          <t>서민금융기관</t>
-        </is>
-      </c>
-      <c r="D11" s="6" t="n">
-        <v>153900</v>
-      </c>
-      <c r="E11" s="6" t="n">
-        <v>149600</v>
-      </c>
-      <c r="F11" s="6" t="n">
-        <v>158200</v>
-      </c>
-      <c r="G11" s="6" t="n">
-        <v>461700</v>
-      </c>
-      <c r="H11" s="6" t="n">
-        <v>300000</v>
-      </c>
-      <c r="I11" s="6" t="n">
-        <v>923400</v>
-      </c>
-      <c r="J11" s="6" t="n">
-        <v>1223400</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="7" t="inlineStr">
+      <c r="A11" s="7" t="inlineStr">
         <is>
           <t>합계</t>
         </is>
       </c>
-      <c r="B12" s="8" t="n"/>
-      <c r="C12" s="8" t="n"/>
-      <c r="D12" s="9" t="n">
-        <v>3233400</v>
-      </c>
-      <c r="E12" s="9" t="n">
-        <v>3268700</v>
-      </c>
-      <c r="F12" s="9" t="n">
-        <v>3256700</v>
-      </c>
-      <c r="G12" s="9" t="n">
-        <v>9758800</v>
-      </c>
-      <c r="H12" s="9" t="n">
-        <v>1800000</v>
-      </c>
-      <c r="I12" s="9" t="n">
-        <v>19517600</v>
-      </c>
-      <c r="J12" s="9" t="n">
-        <v>21317600</v>
+      <c r="B11" s="8" t="n"/>
+      <c r="C11" s="8" t="n"/>
+      <c r="D11" s="9" t="n">
+        <v>3047000</v>
+      </c>
+      <c r="E11" s="9" t="n">
+        <v>3077000</v>
+      </c>
+      <c r="F11" s="9" t="n">
+        <v>3068400</v>
+      </c>
+      <c r="G11" s="9" t="n">
+        <v>9192400</v>
+      </c>
+      <c r="H11" s="9" t="n">
+        <v>1500000</v>
+      </c>
+      <c r="I11" s="9" t="n">
+        <v>18384800</v>
+      </c>
+      <c r="J11" s="9" t="n">
+        <v>19884800</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A12:C12"/>
+    <mergeCell ref="A11:C11"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/backend/src/main/resources/db/seed/files/account-info-fee-precheck.xlsx
+++ b/backend/src/main/resources/db/seed/files/account-info-fee-precheck.xlsx
@@ -7,8 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="기관별 회비" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="산정 기준" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="기관별 분담 회비" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="분담 기준" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -85,7 +85,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -97,11 +97,13 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="4" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="10" fontId="4" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -468,7 +470,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J11"/>
+  <dimension ref="A1:K11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -478,9 +480,10 @@
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="13" customWidth="1" min="6" max="6"/>
     <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="18" customWidth="1" min="9" max="9"/>
-    <col width="16" customWidth="1" min="10" max="10"/>
+    <col width="11" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="16" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -493,7 +496,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>실적 기간: 3분기(7~9월) 계좌정보 통합조회 건수 · 부과 대상: 4분기 회비 · 단위: 건, 원(부가세 별도)</t>
+          <t>4분기 회비 총액 50,000,000원을 참가기관이 분담합니다. 균등분담분 30%는 기관 수로 똑같이, 실적분담분 70%는 3분기(7~9월) 실적 비율로 나눕니다. 단위: 건, 원(부가세 별도)</t>
         </is>
       </c>
     </row>
@@ -542,17 +545,22 @@
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>기본회비</t>
+          <t>실적 비율</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>실적회비(건당 2원)</t>
+          <t>균등분담액</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t>4분기 총 회비</t>
+          <t>실적분담액</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="inlineStr">
+        <is>
+          <t>4분기 분담 회비</t>
         </is>
       </c>
     </row>
@@ -584,14 +592,17 @@
       <c r="G6" s="6" t="n">
         <v>3894300</v>
       </c>
-      <c r="H6" s="6" t="n">
-        <v>300000</v>
+      <c r="H6" s="7" t="n">
+        <v>0.4236434445846569</v>
       </c>
       <c r="I6" s="6" t="n">
-        <v>7788600</v>
+        <v>3000000</v>
       </c>
       <c r="J6" s="6" t="n">
-        <v>8088600</v>
+        <v>14827523</v>
+      </c>
+      <c r="K6" s="6" t="n">
+        <v>17827523</v>
       </c>
     </row>
     <row r="7">
@@ -622,14 +633,17 @@
       <c r="G7" s="6" t="n">
         <v>3316600</v>
       </c>
-      <c r="H7" s="6" t="n">
-        <v>300000</v>
+      <c r="H7" s="7" t="n">
+        <v>0.360798050563509</v>
       </c>
       <c r="I7" s="6" t="n">
-        <v>6633200</v>
+        <v>3000000</v>
       </c>
       <c r="J7" s="6" t="n">
-        <v>6933200</v>
+        <v>12627931</v>
+      </c>
+      <c r="K7" s="6" t="n">
+        <v>15627931</v>
       </c>
     </row>
     <row r="8">
@@ -660,14 +674,17 @@
       <c r="G8" s="6" t="n">
         <v>1232700</v>
       </c>
-      <c r="H8" s="6" t="n">
-        <v>300000</v>
+      <c r="H8" s="7" t="n">
+        <v>0.1340999086201645</v>
       </c>
       <c r="I8" s="6" t="n">
-        <v>2465400</v>
+        <v>3000000</v>
       </c>
       <c r="J8" s="6" t="n">
-        <v>2765400</v>
+        <v>4693496</v>
+      </c>
+      <c r="K8" s="6" t="n">
+        <v>7693496</v>
       </c>
     </row>
     <row r="9">
@@ -698,14 +715,17 @@
       <c r="G9" s="6" t="n">
         <v>287100</v>
       </c>
-      <c r="H9" s="6" t="n">
-        <v>300000</v>
+      <c r="H9" s="7" t="n">
+        <v>0.03123232235324834</v>
       </c>
       <c r="I9" s="6" t="n">
-        <v>574200</v>
+        <v>3000000</v>
       </c>
       <c r="J9" s="6" t="n">
-        <v>874200</v>
+        <v>1093131</v>
+      </c>
+      <c r="K9" s="6" t="n">
+        <v>4093131</v>
       </c>
     </row>
     <row r="10">
@@ -736,44 +756,50 @@
       <c r="G10" s="6" t="n">
         <v>461700</v>
       </c>
-      <c r="H10" s="6" t="n">
-        <v>300000</v>
+      <c r="H10" s="7" t="n">
+        <v>0.0502262738784213</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>923400</v>
+        <v>3000000</v>
       </c>
       <c r="J10" s="6" t="n">
-        <v>1223400</v>
+        <v>1757919</v>
+      </c>
+      <c r="K10" s="6" t="n">
+        <v>4757919</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="7" t="inlineStr">
+      <c r="A11" s="8" t="inlineStr">
         <is>
           <t>합계</t>
         </is>
       </c>
-      <c r="B11" s="8" t="n"/>
-      <c r="C11" s="8" t="n"/>
-      <c r="D11" s="9" t="n">
+      <c r="B11" s="9" t="n"/>
+      <c r="C11" s="9" t="n"/>
+      <c r="D11" s="10" t="n">
         <v>3047000</v>
       </c>
-      <c r="E11" s="9" t="n">
+      <c r="E11" s="10" t="n">
         <v>3077000</v>
       </c>
-      <c r="F11" s="9" t="n">
+      <c r="F11" s="10" t="n">
         <v>3068400</v>
       </c>
-      <c r="G11" s="9" t="n">
+      <c r="G11" s="10" t="n">
         <v>9192400</v>
       </c>
-      <c r="H11" s="9" t="n">
-        <v>1500000</v>
-      </c>
-      <c r="I11" s="9" t="n">
-        <v>18384800</v>
-      </c>
-      <c r="J11" s="9" t="n">
-        <v>19884800</v>
+      <c r="H11" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="I11" s="10" t="n">
+        <v>15000000</v>
+      </c>
+      <c r="J11" s="10" t="n">
+        <v>35000000</v>
+      </c>
+      <c r="K11" s="10" t="n">
+        <v>50000000</v>
       </c>
     </row>
   </sheetData>
@@ -790,27 +816,27 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B12"/>
+  <dimension ref="A1:B13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="80" customWidth="1" min="2" max="2"/>
+    <col width="90" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>4분기 계좌통합관리업무 회비 산정 기준</t>
+          <t>4분기 계좌통합관리업무 회비 분담 기준</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="10" t="inlineStr">
+      <c r="A3" s="12" t="inlineStr">
         <is>
           <t>항목</t>
         </is>
       </c>
-      <c r="B3" s="10" t="inlineStr">
+      <c r="B3" s="12" t="inlineStr">
         <is>
           <t>내용</t>
         </is>
@@ -819,91 +845,103 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>실적 기간</t>
+          <t>4분기 회비 총액</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>3분기(7월 1일 ~ 9월 30일)</t>
+          <t>50,000,000원(부가세 별도)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>실적</t>
+          <t>균등분담분</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>계좌정보 통합조회 응답 건수(기관별, 월별)</t>
+          <t>총액의 30%(15,000,000원)를 참가기관 5곳이 똑같이 나눕니다(기관당 3,000,000원).</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>기본회비</t>
+          <t>실적분담분</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>기관당 분기 300,000원</t>
+          <t>총액의 70%(35,000,000원)를 3분기 실적 비율대로 나눕니다.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>실적회비</t>
+          <t>실적</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>3분기 실적 합계 × 건당 2원</t>
+          <t>3분기(7월 1일 ~ 9월 30일) 계좌정보 통합조회 응답 건수</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>4분기 총 회비</t>
+          <t>실적 비율</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>기본회비 + 실적회비(부가세 별도)</t>
+          <t>기관 3분기 실적 합계 ÷ 전체 참가기관 3분기 실적 합계</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>확인 방법</t>
+          <t>원 단위 끝수</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>의견 회신 화면에서 '의견없음' 또는 '확인 필요'를 고르고, 확인 필요면 문의사항을 적어 주세요.</t>
+          <t>나누고 남은 원 단위 끝수는 실적이 가장 많은 기관에 더합니다.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>확인 방법</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>의견 회신 화면에서 '의견없음' 또는 '확인 필요'를 고르고, 확인 필요면 문의사항을 적어 주세요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
           <t>확정</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>회신 기한 뒤 문의 사항을 반영해 확정 회비를 다시 안내합니다.</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>※ 시연용 샘플 데이터입니다. 실제 산정 기준이 아닙니다.</t>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>※ 시연용 샘플 데이터입니다. 실제 회비 총액·분담 기준이 아닙니다.</t>
         </is>
       </c>
     </row>
